--- a/summer_camps/023_day_camp_staff_health_screening_form--summer_camps.xlsx
+++ b/summer_camps/023_day_camp_staff_health_screening_form--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -575,7 +575,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History Form</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_history_form</t>
+          <t>medical_history_form_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History Form 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emergency_contact_information_form</t>
+          <t>emergency_contact_information_form_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Emergency Contact Information</t>
+          <t>Emergency Contact Information Form 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_history_form</t>
+          <t>medical_history_form_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History Form 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -912,8 +912,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,12 +941,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'peanuts'}</t>
+          <t>peanuts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Peanuts'}</t>
+          <t>Peanuts</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'tree_nuts'}</t>
+          <t>tree_nuts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Tree Nuts'}</t>
+          <t>Tree Nuts</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'cleared'}</t>
+          <t>cleared</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Cleared'}</t>
+          <t>Cleared</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_cleared'}</t>
+          <t>not_cleared</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Not Cleared'}</t>
+          <t>Not Cleared</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'request'}</t>
+          <t>request</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Request'}</t>
+          <t>Request</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'not_request'}</t>
+          <t>not_request</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Not Request'}</t>
+          <t>Not Request</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_none}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': None}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'medication_1'}</t>
+          <t>medication_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Medication 1'}</t>
+          <t>Medication 1</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'medication_2'}</t>
+          <t>medication_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Medication 2'}</t>
+          <t>Medication 2</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'medication_3'}</t>
+          <t>medication_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Medication 3'}</t>
+          <t>Medication 3</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
